--- a/results/04_final_refined_daily_hydroclimate_data/601/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Max_Temperature_timeseries.xlsx
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -582,7 +582,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -708,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -750,7 +750,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="27" spans="1:4">
